--- a/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 0,0</t>
+          <t>-8,87; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,0</t>
+          <t>-8,94; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,0</t>
+          <t>-5,38; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,0</t>
+          <t>-4,83; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,9</t>
+          <t>-6,22; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 1,22</t>
+          <t>-7,67; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,0</t>
+          <t>-8,69; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,0</t>
+          <t>-7,25; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,79</t>
+          <t>-4,57; 1,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,5</t>
+          <t>-5,2; 0,41</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 1,21</t>
+          <t>-11,16; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 6,05</t>
+          <t>-7,96; 7,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,65</t>
+          <t>-6,83; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,21</t>
+          <t>-4,64; 4,38</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 6,21</t>
+          <t>-9,23; 6,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 0,0</t>
+          <t>-16,73; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 7,94</t>
+          <t>-3,73; 8,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 3,54</t>
+          <t>-5,58; 5,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,85</t>
+          <t>-3,45; 5,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,81</t>
+          <t>-6,45; 0,82</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,06</t>
+          <t>-2,84; 2,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,64</t>
+          <t>-3,56; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,25</t>
+          <t>-3,45; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,18</t>
+          <t>-3,64; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,24</t>
+          <t>-2,32; 1,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,4</t>
+          <t>-2,72; 0,47</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,66; 184,84</t>
+          <t>-89,82; 174,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,65</t>
+          <t>-99,03; 273,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 148,45</t>
+          <t>-75,65; 113,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,76; 71,15</t>
+          <t>-88,57; 74,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,0</t>
+          <t>-8,86; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,0</t>
+          <t>-9,88; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-4,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,88</t>
+          <t>-6,32; 4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 1,72</t>
+          <t>-9,06; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,0</t>
+          <t>-8,1; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 0,0</t>
+          <t>-6,87; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,76</t>
+          <t>-4,52; 1,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,41</t>
+          <t>-5,24; 0,6</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 1,38</t>
+          <t>-9,71; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 7,0</t>
+          <t>-9,77; 5,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,65</t>
+          <t>-6,48; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,38</t>
+          <t>-4,53; 4,13</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,29</t>
+          <t>-9,16; 6,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 0,0</t>
+          <t>-17,84; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 8,33</t>
+          <t>-3,5; 8,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 5,05</t>
+          <t>-5,48; 3,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,61</t>
+          <t>-3,97; 5,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,82</t>
+          <t>-6,87; 0,83</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,12</t>
+          <t>-2,6; 2,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,87</t>
+          <t>-3,48; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,31</t>
+          <t>-3,52; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,16</t>
+          <t>-3,68; 1,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,08</t>
+          <t>-2,27; 1,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,47</t>
+          <t>-2,77; 0,39</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,82; 174,06</t>
+          <t>-90,89; 192,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-99,03; 273,95</t>
+          <t>-100,0; 215,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 113,53</t>
+          <t>-75,71; 118,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 74,59</t>
+          <t>-90,74; 48,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Habitat-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,93</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,41; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,68; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,0</t>
+          <t>-3,72; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-1,85</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,55</t>
+          <t>-7,35; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,52</t>
+          <t>-7,32; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,0</t>
+          <t>-6,63; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,0</t>
+          <t>-8,84; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,77</t>
+          <t>-5,17; 1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,6</t>
+          <t>-5,84; 0,5</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-14,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-61,56%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1,54</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,29; 1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>-7,85; 6,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 5,77</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,64</t>
+          <t>-6,55; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 4,13</t>
+          <t>-4,11; 4,21</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-69,57%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,71%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-69,57%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-3,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,08</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 6,37</t>
+          <t>-3,61; 7,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 0,0</t>
+          <t>-5,58; 3,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 8,04</t>
+          <t>-9,22; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,52</t>
+          <t>-15,39; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,35</t>
+          <t>-3,4; 5,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,83</t>
+          <t>-7,18; 0,81</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>128,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-3,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>128,61%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,84</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,31</t>
+          <t>-3,32; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,71</t>
+          <t>-3,76; 1,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,31</t>
+          <t>-2,76; 2,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,2</t>
+          <t>-3,7; 0,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,17</t>
+          <t>-2,28; 1,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,39</t>
+          <t>-2,65; 0,4</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-37,62%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-3,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-56,94%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-37,62%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-43,78%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,66; 184,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 240,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 192,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 118,14</t>
+          <t>-74,77; 148,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-90,74; 48,05</t>
+          <t>-87,76; 71,15</t>
         </is>
       </c>
     </row>
